--- a/output/pdf_financials_xlsx/BER.H.xlsx
+++ b/output/pdf_financials_xlsx/BER.H.xlsx
@@ -1280,10 +1280,10 @@
         <v>-0.032333</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="17">
@@ -1556,10 +1556,10 @@
         <v>-0.032333</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="21">
@@ -1722,10 +1722,10 @@
         <v>-0.032333</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="24">
@@ -1852,64 +1852,48 @@
         </is>
       </c>
       <c r="C26" s="3" t="n">
-        <v>9.235625000000001</v>
+        <v>10.007625</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>12.989475</v>
+        <v>13.901324</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>17.19025</v>
-      </c>
-      <c r="F26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>19.357625</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>19.357625</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>19.357625</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>19.357625</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>4.5583</v>
+        <v>3.871563</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>4.834</v>
+        <v>4.345231</v>
       </c>
       <c r="K26" s="1" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="P26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="L26" s="3" t="n">
+        <v>5.798552</v>
+      </c>
+      <c r="M26" s="3" t="n">
+        <v>5.798552</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>5.798552</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>5.798552</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>8.966647999999999</v>
       </c>
     </row>
     <row r="27">
@@ -1962,10 +1946,10 @@
         <v>-0.032333</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="28">
@@ -2074,10 +2058,10 @@
         <v>-0.032333</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="30">
@@ -2212,10 +2196,10 @@
         <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5610,7 +5594,7 @@
         </is>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>0.00256</v>
       </c>
       <c r="M92" s="3" t="n">
         <v>0</v>
@@ -11503,7 +11487,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -24103,10 +24091,10 @@
         </is>
       </c>
       <c r="R177" s="5" t="n">
-        <v>0.050404</v>
+        <v>-0.050404</v>
       </c>
       <c r="S177" s="5" t="n">
-        <v>0.015368</v>
+        <v>-0.015368</v>
       </c>
     </row>
     <row r="178">

--- a/output/pdf_financials_xlsx/BER.H.xlsx
+++ b/output/pdf_financials_xlsx/BER.H.xlsx
@@ -1053,10 +1053,10 @@
         <v>0</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000362</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000815</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>0</v>
@@ -1943,10 +1943,10 @@
         <v>-0.07337299999999999</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-0.032333</v>
+        <v>-0.031971</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-0.050404</v>
+        <v>-0.049589</v>
       </c>
       <c r="P27" s="3" t="n">
         <v>-0.015368</v>
@@ -2055,10 +2055,10 @@
         <v>-0.07337299999999999</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-0.032333</v>
+        <v>-0.031971</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-0.050404</v>
+        <v>-0.049589</v>
       </c>
       <c r="P29" s="3" t="n">
         <v>-0.015368</v>
@@ -2298,31 +2298,31 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.897414</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.287145</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.341439</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.203512</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.127215</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.072577</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011567</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.014511</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="K34" s="1" t="inlineStr">
         <is>
@@ -2330,19 +2330,19 @@
         </is>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.001455</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.008789</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.001693</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.017789</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.007825</v>
       </c>
     </row>
     <row r="35">
@@ -2406,31 +2406,31 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.897414</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.287145</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.341439</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.203512</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.127215</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.072577</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011567</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.014511</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.0108</v>
       </c>
       <c r="K36" s="1" t="inlineStr">
         <is>
@@ -2438,19 +2438,19 @@
         </is>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.001455</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.008789</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.001693</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.017789</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.007825</v>
       </c>
     </row>
     <row r="37">
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.897414</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.981145</v>
+        <v>0.694</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0</v>
@@ -3089,13 +3089,13 @@
         <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.008789</v>
+        <v>0</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.004206</v>
+        <v>0.002513</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.020043</v>
+        <v>0.002254</v>
       </c>
       <c r="P48" s="3" t="n">
         <v>0</v>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -11584,7 +11584,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -13315,7 +13315,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
@@ -23567,7 +23567,7 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -24653,7 +24653,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">

--- a/output/pdf_financials_xlsx/BER.H.xlsx
+++ b/output/pdf_financials_xlsx/BER.H.xlsx
@@ -6556,7 +6556,7 @@
         <v>0</v>
       </c>
       <c r="C110" s="3" t="n">
-        <v>0</v>
+        <v>0.036664</v>
       </c>
       <c r="D110" s="3" t="n">
         <v>0</v>
@@ -22117,7 +22117,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E156" t="inlineStr">
         <is>
           <t>-</t>
